--- a/Validation_Report.xlsx
+++ b/Validation_Report.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,12 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,14 +439,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="41" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +461,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Expected Pipe No (from Master)</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
@@ -480,17 +481,12 @@
           <t>N26001361</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>N26001361</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>✅ MATCHED</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>✅ TESTED - MATCHED</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>Test conducted using Pipe No: N26001361</t>
         </is>
@@ -507,17 +503,12 @@
           <t>N26001365</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>N26001365</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>✅ MATCHED</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>✅ TESTED - MATCHED</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>Test conducted using Pipe No: N26001365</t>
         </is>
@@ -534,17 +525,12 @@
           <t>N26001371</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>N26001371</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>✅ MATCHED</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>✅ TESTED - MATCHED</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Test conducted using Pipe No: N26001371</t>
         </is>
@@ -561,19 +547,1026 @@
           <t>N26001372</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>N26001372</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>✅ MATCHED</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>✅ TESTED - MATCHED</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Test conducted using Pipe No: N26001372</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>25303797</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Heat No 25303797 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>25203477</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Heat No 25203477 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>25204008</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Heat No 25204008 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>25203345</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Heat No 25203345 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>25103824</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Heat No 25103824 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>25103825</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Heat No 25103825 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>25103827</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Heat No 25103827 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>25204012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Heat No 25204012 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>25103595</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Heat No 25103595 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>25204002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Heat No 25204002 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>65123818</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Heat No 65123818 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>65123513</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Heat No 65123513 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>25103829</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Heat No 25103829 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>25203479</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Heat No 25203479 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>25304003</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Heat No 25304003 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>25103739</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Heat No 25103739 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>25304284</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Heat No 25304284 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>25103920</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Heat No 25103920 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>25103741</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Heat No 25103741 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>65123515</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Heat No 65123515 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25304441</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Heat No 25304441 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>25304283</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Heat No 25304283 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>25203476</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Heat No 25203476 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>65123819</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Heat No 65123819 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>65123820</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Heat No 65123820 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>65122835</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Heat No 65122835 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>25104184</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Heat No 25104184 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>25303944</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Heat No 25303944 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>25304001</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Heat No 25304001 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>25203481</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Heat No 25203481 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>65123511</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Heat No 65123511 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>25304000</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Heat No 25304000 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>25303802</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Heat No 25303802 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>25204001</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Heat No 25204001 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>25204007</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Heat No 25204007 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>25304002</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Heat No 25304002 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>25203339</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Heat No 25203339 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>25203620</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Heat No 25203620 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>25103661</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Heat No 25103661 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>25304442</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Heat No 25304442 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>25204011</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Heat No 25204011 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>65123817</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Heat No 65123817 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>25103477</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Heat No 25103477 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>25203475</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Heat No 25203475 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>25204014</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Heat No 25204014 was not tested</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>25203626</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NOT TESTED</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>❌ NOT TESTED</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Heat No 25203626 was not tested</t>
         </is>
       </c>
     </row>
